--- a/Entry List 10_40am.xlsx
+++ b/Entry List 10_40am.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2653D32C-E38E-41A4-ABB8-6028FF8FA09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B44C7DB-2D82-441C-A32D-627A06D81359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -925,13 +925,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -951,12 +945,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -988,6 +976,18 @@
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1066,6 +1066,404 @@
         <top style="thin">
           <color auto="1"/>
         </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
         <bottom/>
       </border>
       <extLst>
@@ -1091,7 +1489,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
         </left>
@@ -1101,9 +1499,15 @@
         <top style="thin">
           <color auto="1"/>
         </top>
-        <bottom style="medium">
+        <bottom style="thin">
           <color auto="1"/>
         </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1120,410 +1524,6 @@
         <bottom style="medium">
           <color auto="1"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1590,29 +1590,29 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB2F57D0-72E5-447F-A3B0-45114F2DF106}" name="Table1" displayName="Table1" ref="A1:M85" totalsRowCount="1" headerRowDxfId="32">
   <autoFilter ref="A1:M84" xr:uid="{CB2F57D0-72E5-447F-A3B0-45114F2DF106}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{2E76C30E-1712-40BE-9549-71C9C93B502D}" name="Name" totalsRowLabel="Total" dataDxfId="31" totalsRowDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{B49483E4-5D8F-40B6-8641-DD9E65DC8898}" name="Club" dataDxfId="30" totalsRowDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{059F9E1A-99DD-4E87-BCC2-21ED7DCBC75C}" name="Paid" dataDxfId="6" totalsRowDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{6D81A917-4325-4EEA-A94E-463FBA3CD2DE}" name="Registered League" dataDxfId="29" totalsRowDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{77DB4597-4DE2-49A3-8551-3945B9C26A0F}" name="Current League Rank" dataDxfId="28" totalsRowDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{28EE5F78-650B-40EA-9D3E-86070DEB6E33}" name="SATTB Rank" dataDxfId="27" totalsRowDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{B0512E74-2097-4749-8D71-028F16552145}" name="Maties Rank" dataDxfId="26" totalsRowDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{33263E04-7CFE-40B1-A063-335CFE82FBBA}" name="2nd &amp; Below" totalsRowFunction="custom" dataDxfId="25" totalsRowDxfId="13">
+    <tableColumn id="1" xr3:uid="{2E76C30E-1712-40BE-9549-71C9C93B502D}" name="Name" totalsRowLabel="Total" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{B49483E4-5D8F-40B6-8641-DD9E65DC8898}" name="Club" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="13" xr3:uid="{059F9E1A-99DD-4E87-BCC2-21ED7DCBC75C}" name="Paid" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{6D81A917-4325-4EEA-A94E-463FBA3CD2DE}" name="Registered League" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{77DB4597-4DE2-49A3-8551-3945B9C26A0F}" name="Current League Rank" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{28EE5F78-650B-40EA-9D3E-86070DEB6E33}" name="SATTB Rank" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{B0512E74-2097-4749-8D71-028F16552145}" name="Maties Rank" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{33263E04-7CFE-40B1-A063-335CFE82FBBA}" name="2nd &amp; Below" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="16">
       <totalsRowFormula>COUNTIF(Table1[2nd &amp; Below],TRUE)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0F990E8B-E4C9-4D0D-9CC5-A6D55E12654F}" name="5th &amp; Below" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="12">
+    <tableColumn id="5" xr3:uid="{0F990E8B-E4C9-4D0D-9CC5-A6D55E12654F}" name="5th &amp; Below" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="14">
       <totalsRowFormula>COUNTIF(Table1[5th &amp; Below],TRUE)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E3251279-4988-46EB-AD20-00F1E80654F1}" name="Senior Women" totalsRowFunction="custom" dataDxfId="23" totalsRowDxfId="11">
+    <tableColumn id="6" xr3:uid="{E3251279-4988-46EB-AD20-00F1E80654F1}" name="Senior Women" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="12">
       <totalsRowFormula>COUNTIF(Table1[Senior Women],TRUE)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D79D3630-5FB1-4D9E-A424-AC37ECA2C0CD}" name="Senior Men" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="10">
+    <tableColumn id="7" xr3:uid="{D79D3630-5FB1-4D9E-A424-AC37ECA2C0CD}" name="Senior Men" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="10">
       <totalsRowFormula>COUNTIF(Table1[Senior Men],TRUE)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC7ED2C1-E830-49D6-B996-8C9D9B21457E}" name="Column1" dataDxfId="21" totalsRowDxfId="9">
+    <tableColumn id="11" xr3:uid="{AC7ED2C1-E830-49D6-B996-8C9D9B21457E}" name="Column1" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{524892D6-ACD8-434C-B13E-1FC70A4B293F}" name="Column2" totalsRowFunction="custom" dataDxfId="20" totalsRowDxfId="8">
+    <tableColumn id="12" xr3:uid="{524892D6-ACD8-434C-B13E-1FC70A4B293F}" name="Column2" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Column1]]=1,120,180)</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table1[Column2])</totalsRowFormula>
     </tableColumn>
@@ -1947,11 +1947,13 @@
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="7" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" hidden="1" customWidth="1"/>
+    <col min="5" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
     <col min="10" max="10" width="16.42578125" customWidth="1"/>
     <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="13" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2002,8 +2004,8 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31" t="b">
-        <v>0</v>
+      <c r="C2" s="27" t="b">
+        <v>1</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -2039,7 +2041,7 @@
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="32" t="b">
+      <c r="C3" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D3" s="3"/>
@@ -2074,8 +2076,8 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="32" t="b">
-        <v>0</v>
+      <c r="C4" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2111,7 +2113,7 @@
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="32" t="b">
+      <c r="C5" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -2152,7 +2154,7 @@
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="32" t="b">
+      <c r="C6" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D6" s="3"/>
@@ -2189,7 +2191,7 @@
       <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="32" t="b">
+      <c r="C7" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2230,7 +2232,7 @@
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="32" t="b">
+      <c r="C8" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2271,7 +2273,7 @@
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="32" t="b">
+      <c r="C9" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -2312,7 +2314,7 @@
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="32" t="b">
+      <c r="C10" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -2353,7 +2355,7 @@
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="32" t="b">
+      <c r="C11" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -2394,7 +2396,7 @@
       <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="32" t="b">
+      <c r="C12" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -2435,7 +2437,7 @@
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="32" t="b">
+      <c r="C13" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -2476,7 +2478,7 @@
       <c r="B14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="32" t="b">
+      <c r="C14" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2515,7 +2517,7 @@
       <c r="B15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="32" t="b">
+      <c r="C15" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -2554,7 +2556,7 @@
       <c r="B16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="32" t="b">
+      <c r="C16" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -2593,7 +2595,7 @@
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="32" t="b">
+      <c r="C17" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D17" s="3"/>
@@ -2630,7 +2632,7 @@
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="32" t="b">
+      <c r="C18" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -2671,7 +2673,7 @@
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="32" t="b">
+      <c r="C19" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -2710,7 +2712,7 @@
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="32" t="b">
+      <c r="C20" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -2751,7 +2753,7 @@
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="32" t="b">
+      <c r="C21" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -2792,7 +2794,7 @@
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="32" t="b">
+      <c r="C22" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -2833,7 +2835,7 @@
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="32" t="b">
+      <c r="C23" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -2874,7 +2876,7 @@
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="32" t="b">
+      <c r="C24" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D24" s="3"/>
@@ -2909,7 +2911,7 @@
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="32" t="b">
+      <c r="C25" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -2950,7 +2952,7 @@
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="32" t="b">
+      <c r="C26" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D26" s="3"/>
@@ -2985,7 +2987,7 @@
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="32" t="b">
+      <c r="C27" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -3024,7 +3026,7 @@
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="32" t="b">
+      <c r="C28" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -3065,7 +3067,7 @@
       <c r="B29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="32" t="b">
+      <c r="C29" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -3106,7 +3108,7 @@
       <c r="B30" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="32" t="b">
+      <c r="C30" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -3147,7 +3149,7 @@
       <c r="B31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="32" t="b">
+      <c r="C31" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -3186,7 +3188,7 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="32" t="b">
+      <c r="C32" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D32" s="3"/>
@@ -3221,7 +3223,7 @@
       <c r="B33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="32" t="b">
+      <c r="C33" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -3262,7 +3264,7 @@
       <c r="B34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="32" t="b">
+      <c r="C34" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -3301,7 +3303,7 @@
       <c r="B35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="32" t="b">
+      <c r="C35" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -3342,7 +3344,7 @@
       <c r="B36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="32" t="b">
+      <c r="C36" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -3381,7 +3383,7 @@
       <c r="B37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="32" t="b">
+      <c r="C37" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -3420,7 +3422,7 @@
       <c r="B38" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="32" t="b">
+      <c r="C38" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -3461,7 +3463,7 @@
       <c r="B39" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="32" t="b">
+      <c r="C39" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -3502,7 +3504,7 @@
       <c r="B40" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="32" t="b">
+      <c r="C40" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -3541,7 +3543,7 @@
       <c r="B41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="32" t="b">
+      <c r="C41" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D41" s="3" t="s">
@@ -3582,7 +3584,7 @@
       <c r="B42" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="32" t="b">
+      <c r="C42" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -3623,7 +3625,7 @@
       <c r="B43" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="32" t="b">
+      <c r="C43" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -3664,7 +3666,7 @@
       <c r="B44" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="32" t="b">
+      <c r="C44" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -3705,7 +3707,7 @@
       <c r="B45" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="32" t="b">
+      <c r="C45" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D45" s="3" t="s">
@@ -3746,7 +3748,7 @@
       <c r="B46" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="32" t="b">
+      <c r="C46" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -3787,7 +3789,7 @@
       <c r="B47" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="32" t="b">
+      <c r="C47" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -3826,7 +3828,7 @@
       <c r="B48" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="32" t="b">
+      <c r="C48" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -3865,7 +3867,7 @@
       <c r="B49" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="32" t="b">
+      <c r="C49" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -3904,7 +3906,7 @@
       <c r="B50" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="32" t="b">
+      <c r="C50" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -3943,7 +3945,7 @@
       <c r="B51" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="32" t="b">
+      <c r="C51" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D51" s="3"/>
@@ -3978,7 +3980,7 @@
       <c r="B52" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C52" s="32" t="b">
+      <c r="C52" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -4019,7 +4021,7 @@
       <c r="B53" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="32" t="b">
+      <c r="C53" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -4060,7 +4062,7 @@
       <c r="B54" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="32" t="b">
+      <c r="C54" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -4099,7 +4101,7 @@
       <c r="B55" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="32" t="b">
+      <c r="C55" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -4138,7 +4140,7 @@
         <v>67</v>
       </c>
       <c r="B56" s="3"/>
-      <c r="C56" s="32" t="b">
+      <c r="C56" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D56" s="3"/>
@@ -4173,7 +4175,7 @@
       <c r="B57" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C57" s="32" t="b">
+      <c r="C57" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -4212,8 +4214,8 @@
       <c r="B58" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="32" t="b">
-        <v>0</v>
+      <c r="C58" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>186</v>
@@ -4251,8 +4253,8 @@
       <c r="B59" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C59" s="32" t="b">
-        <v>0</v>
+      <c r="C59" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>186</v>
@@ -4292,8 +4294,8 @@
       <c r="B60" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C60" s="32" t="b">
-        <v>0</v>
+      <c r="C60" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>186</v>
@@ -4333,8 +4335,8 @@
       <c r="B61" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C61" s="32" t="b">
-        <v>0</v>
+      <c r="C61" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>186</v>
@@ -4372,8 +4374,8 @@
       <c r="B62" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C62" s="32" t="b">
-        <v>0</v>
+      <c r="C62" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -4409,8 +4411,8 @@
       <c r="B63" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C63" s="32" t="b">
-        <v>0</v>
+      <c r="C63" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -4444,8 +4446,8 @@
       <c r="B64" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C64" s="32" t="b">
-        <v>0</v>
+      <c r="C64" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -4481,8 +4483,8 @@
       <c r="B65" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="32" t="b">
-        <v>0</v>
+      <c r="C65" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -4518,8 +4520,8 @@
       <c r="B66" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C66" s="32" t="b">
-        <v>0</v>
+      <c r="C66" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>180</v>
@@ -4559,8 +4561,8 @@
       <c r="B67" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C67" s="32" t="b">
-        <v>0</v>
+      <c r="C67" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -4596,8 +4598,8 @@
       <c r="B68" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="32" t="b">
-        <v>0</v>
+      <c r="C68" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>181</v>
@@ -4635,7 +4637,7 @@
       <c r="B69" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="32" t="b">
+      <c r="C69" s="28" t="b">
         <v>1</v>
       </c>
       <c r="D69" s="3"/>
@@ -4672,7 +4674,7 @@
       <c r="B70" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C70" s="32" t="b">
+      <c r="C70" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -4713,7 +4715,7 @@
       <c r="B71" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C71" s="32" t="b">
+      <c r="C71" s="28" t="b">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -4752,8 +4754,8 @@
       <c r="B72" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C72" s="32" t="b">
-        <v>0</v>
+      <c r="C72" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>186</v>
@@ -4793,8 +4795,8 @@
       <c r="B73" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C73" s="32" t="b">
-        <v>0</v>
+      <c r="C73" s="28" t="b">
+        <v>1</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>180</v>
@@ -4834,7 +4836,7 @@
       <c r="B74" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C74" s="33" t="b">
+      <c r="C74" s="29" t="b">
         <v>0</v>
       </c>
       <c r="D74" s="12" t="s">
@@ -4875,8 +4877,8 @@
       <c r="B75" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="C75" s="33" t="b">
-        <v>0</v>
+      <c r="C75" s="29" t="b">
+        <v>1</v>
       </c>
       <c r="D75" s="12"/>
       <c r="E75" s="12"/>
@@ -4910,8 +4912,8 @@
       <c r="B76" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="C76" s="33" t="b">
-        <v>0</v>
+      <c r="C76" s="29" t="b">
+        <v>1</v>
       </c>
       <c r="D76" s="12"/>
       <c r="E76" s="12"/>
@@ -4945,8 +4947,8 @@
       <c r="B77" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="C77" s="33" t="b">
-        <v>0</v>
+      <c r="C77" s="29" t="b">
+        <v>1</v>
       </c>
       <c r="D77" s="12"/>
       <c r="E77" s="12"/>
@@ -4980,7 +4982,7 @@
       <c r="B78" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="C78" s="33" t="b">
+      <c r="C78" s="29" t="b">
         <v>0</v>
       </c>
       <c r="D78" s="12"/>
@@ -5009,36 +5011,36 @@
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="30" t="s">
+      <c r="A79" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="B79" s="30" t="s">
+      <c r="B79" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="C79" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="D79" s="28"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="28"/>
-      <c r="G79" s="28"/>
-      <c r="H79" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I79" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79" s="28">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M79" s="28">
+      <c r="C79" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" s="24"/>
+      <c r="E79" s="24"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="24"/>
+      <c r="H79" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" s="24">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M79" s="24">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
@@ -5050,8 +5052,8 @@
       <c r="B80" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C80" s="33" t="b">
-        <v>0</v>
+      <c r="C80" s="29" t="b">
+        <v>1</v>
       </c>
       <c r="D80" s="12"/>
       <c r="E80" s="12"/>
@@ -5085,7 +5087,7 @@
       <c r="B81" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="33" t="b">
+      <c r="C81" s="29" t="b">
         <v>0</v>
       </c>
       <c r="D81" s="12"/>
@@ -5120,8 +5122,8 @@
       <c r="B82" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C82" s="33" t="b">
-        <v>0</v>
+      <c r="C82" s="29" t="b">
+        <v>1</v>
       </c>
       <c r="D82" s="12"/>
       <c r="E82" s="12"/>
@@ -5155,8 +5157,8 @@
       <c r="B83" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="33" t="b">
-        <v>0</v>
+      <c r="C83" s="29" t="b">
+        <v>1</v>
       </c>
       <c r="D83" s="12"/>
       <c r="E83" s="12"/>
@@ -5190,7 +5192,7 @@
       <c r="B84" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C84" s="33" t="b">
+      <c r="C84" s="29" t="b">
         <v>0</v>
       </c>
       <c r="D84" s="12"/>
@@ -5828,29 +5830,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="22"/>
+    <col min="2" max="2" width="9.140625" style="20"/>
     <col min="3" max="10" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="18" t="s">
         <v>95</v>
       </c>
       <c r="C2" s="14">
@@ -5882,49 +5884,49 @@
       <c r="A3" s="15">
         <v>46171</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="19">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
     </row>
     <row r="4" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <v>46171</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="19">
         <v>0.80208333333333337</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="17" t="s">
         <v>198</v>
       </c>
       <c r="K4" s="1"/>
@@ -5935,31 +5937,31 @@
       <c r="A5" s="15">
         <v>46171</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>0.84375</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="17" t="s">
         <v>198</v>
       </c>
       <c r="K5" s="1"/>
@@ -5972,31 +5974,31 @@
       <c r="A6" s="15">
         <v>46171</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="19">
         <v>0.88541666666666663</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="17" t="s">
         <v>198</v>
       </c>
       <c r="K6" s="1"/>
@@ -6007,91 +6009,91 @@
       <c r="A7" s="15">
         <v>46171</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="19">
         <v>0.92708333333333337</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>46172</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="19">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>46172</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="19">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="17" t="s">
         <v>205</v>
       </c>
     </row>
@@ -6099,29 +6101,29 @@
       <c r="A11" s="15">
         <v>46172</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="19">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="17" t="s">
         <v>205</v>
       </c>
     </row>
@@ -6129,31 +6131,31 @@
       <c r="A12" s="15">
         <v>46172</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="19">
         <v>0.47916666666666669</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="J12" s="19" t="s">
+      <c r="J12" s="17" t="s">
         <v>203</v>
       </c>
       <c r="K12" s="1"/>
@@ -6162,22 +6164,22 @@
       <c r="A13" s="15">
         <v>46172</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="19">
         <v>0.60416666666666663</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="17" t="s">
         <v>143</v>
       </c>
       <c r="H13" s="14"/>
@@ -6189,25 +6191,25 @@
       <c r="A14" s="15">
         <v>46172</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="19">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="16" t="s">
         <v>211</v>
       </c>
       <c r="I14" s="14"/>
@@ -6219,31 +6221,31 @@
       <c r="A15" s="15">
         <v>46172</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="19">
         <v>0.6875</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="16" t="s">
         <v>113</v>
       </c>
       <c r="K15" s="1"/>
@@ -6253,31 +6255,31 @@
       <c r="A16" s="15">
         <v>46172</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="19">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="16" t="s">
         <v>134</v>
       </c>
       <c r="K16" s="1"/>
@@ -6287,31 +6289,31 @@
       <c r="A17" s="15">
         <v>46172</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="19">
         <v>0.72916666666666663</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="J17" s="17" t="s">
+      <c r="J17" s="16" t="s">
         <v>162</v>
       </c>
       <c r="K17" s="1"/>
@@ -6321,19 +6323,19 @@
       <c r="A18" s="15">
         <v>46172</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="19">
         <v>0.75</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="16" t="s">
         <v>120</v>
       </c>
       <c r="G18" s="14"/>
@@ -6347,31 +6349,31 @@
       <c r="A19" s="15">
         <v>46172</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="19">
         <v>0.77083333333333337</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="I19" s="19" t="s">
+      <c r="I19" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="J19" s="19" t="s">
+      <c r="J19" s="17" t="s">
         <v>138</v>
       </c>
       <c r="K19" s="1"/>
@@ -6381,25 +6383,25 @@
       <c r="A20" s="15">
         <v>46172</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="19">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
@@ -6407,25 +6409,25 @@
       <c r="A21" s="15">
         <v>46172</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="19">
         <v>0.8125</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
@@ -6433,21 +6435,21 @@
       <c r="A22" s="15">
         <v>46172</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="19">
         <v>0.83333333333333337</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
@@ -6455,21 +6457,21 @@
       <c r="A23" s="15">
         <v>46172</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="19">
         <v>0.85416666666666663</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
@@ -6477,19 +6479,19 @@
       <c r="A24" s="15">
         <v>46172</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="19">
         <v>0.875</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -6497,16 +6499,16 @@
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C26" s="1"/>
@@ -6577,7 +6579,7 @@
     <mergeCell ref="C24:J24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C9:J11 C12:C13 G17:J17 C17:F18 C19:J23 D12:J12 D13:G13 C15:J16 C14:H14 C4:J7">
+  <conditionalFormatting sqref="C4:J7 C9:J11 D12:J12 C12:C13 D13:G13 C14:H14 C15:J16 G17:J17 C17:F18 C19:J23">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="5th">
       <formula>NOT(ISERROR(SEARCH("5th",C4)))</formula>
     </cfRule>

--- a/Entry List 10_40am.xlsx
+++ b/Entry List 10_40am.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B44C7DB-2D82-441C-A32D-627A06D81359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98897C1A-5B74-4F36-ABB2-1B59DA927F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
+    <workbookView xWindow="-20520" yWindow="2025" windowWidth="20640" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="217">
   <si>
     <t>Le Roux Strydom</t>
   </si>
@@ -711,6 +711,9 @@
   </si>
   <si>
     <t>Paid</t>
+  </si>
+  <si>
+    <t>Lunch</t>
   </si>
 </sst>
 </file>
@@ -775,7 +778,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -898,12 +901,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -987,6 +1027,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5826,7 +5875,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4AE9985-8C42-47F9-887C-80BAC08CD96D}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -6102,7 +6151,7 @@
         <v>46172</v>
       </c>
       <c r="B11" s="19">
-        <v>0.41666666666666669</v>
+        <v>0.40625</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>121</v>
@@ -6132,7 +6181,7 @@
         <v>46172</v>
       </c>
       <c r="B12" s="19">
-        <v>0.47916666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>204</v>
@@ -6165,7 +6214,7 @@
         <v>46172</v>
       </c>
       <c r="B13" s="19">
-        <v>0.60416666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>98</v>
@@ -6179,142 +6228,125 @@
       <c r="F13" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="G13" s="17" t="s">
-        <v>143</v>
-      </c>
+      <c r="G13" s="17"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>46172</v>
       </c>
       <c r="B14" s="19">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
+        <v>0.625</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="37"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <v>46172</v>
       </c>
       <c r="B15" s="19">
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>113</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>46172</v>
       </c>
       <c r="B16" s="19">
-        <v>0.70833333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>127</v>
+        <v>212</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>46172</v>
       </c>
       <c r="B17" s="19">
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -6324,84 +6356,92 @@
         <v>46172</v>
       </c>
       <c r="B18" s="19">
-        <v>0.75</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+        <v>158</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>46172</v>
       </c>
       <c r="B19" s="19">
-        <v>0.77083333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>138</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <v>46172</v>
       </c>
       <c r="B20" s="19">
-        <v>0.79166666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
+        <v>166</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>138</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
@@ -6410,19 +6450,19 @@
         <v>46172</v>
       </c>
       <c r="B21" s="19">
-        <v>0.8125</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
@@ -6431,21 +6471,25 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>46172</v>
       </c>
       <c r="B22" s="19">
-        <v>0.83333333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+        <v>168</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>140</v>
+      </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
@@ -6458,13 +6502,13 @@
         <v>46172</v>
       </c>
       <c r="B23" s="19">
-        <v>0.85416666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
@@ -6475,50 +6519,62 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>46172</v>
       </c>
       <c r="B24" s="19">
-        <v>0.875</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="22"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
+    </row>
+    <row r="25" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15">
+        <v>46172</v>
+      </c>
+      <c r="B25" s="19">
+        <v>0.875</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C27" s="1"/>
@@ -6570,16 +6626,27 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="C3:J3"/>
     <mergeCell ref="C9:J9"/>
-    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="C14:J14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:J7 C9:J11 D12:J12 C12:C13 D13:G13 C14:H14 C15:J16 G17:J17 C17:F18 C19:J23">
+  <conditionalFormatting sqref="C4:J7 C9:J11 D12:J12 C12:C14 D13:G13 C15:H15 C16:J17 G18:J18 C18:F19 C20:J24">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="5th">
       <formula>NOT(ISERROR(SEARCH("5th",C4)))</formula>
     </cfRule>

--- a/Entry List 10_40am.xlsx
+++ b/Entry List 10_40am.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98897C1A-5B74-4F36-ABB2-1B59DA927F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B75157-38CD-495C-94F3-566E5435B311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="2025" windowWidth="20640" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="216">
   <si>
     <t>Le Roux Strydom</t>
   </si>
@@ -711,9 +711,6 @@
   </si>
   <si>
     <t>Paid</t>
-  </si>
-  <si>
-    <t>Lunch</t>
   </si>
 </sst>
 </file>
@@ -778,7 +775,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -873,66 +870,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -943,7 +883,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -979,13 +919,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1017,7 +950,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1027,15 +960,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2053,7 +1977,7 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="27" t="b">
+      <c r="C2" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D2" s="2"/>
@@ -2090,7 +2014,7 @@
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="28" t="b">
+      <c r="C3" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D3" s="3"/>
@@ -2125,7 +2049,7 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="28" t="b">
+      <c r="C4" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D4" s="3"/>
@@ -2162,7 +2086,7 @@
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="b">
+      <c r="C5" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -2203,7 +2127,7 @@
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="28" t="b">
+      <c r="C6" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D6" s="3"/>
@@ -2240,7 +2164,7 @@
       <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="28" t="b">
+      <c r="C7" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2281,7 +2205,7 @@
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="28" t="b">
+      <c r="C8" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2322,7 +2246,7 @@
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="28" t="b">
+      <c r="C9" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -2363,7 +2287,7 @@
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="28" t="b">
+      <c r="C10" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -2404,7 +2328,7 @@
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="28" t="b">
+      <c r="C11" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -2445,7 +2369,7 @@
       <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="28" t="b">
+      <c r="C12" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -2486,7 +2410,7 @@
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28" t="b">
+      <c r="C13" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -2527,7 +2451,7 @@
       <c r="B14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28" t="b">
+      <c r="C14" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2566,7 +2490,7 @@
       <c r="B15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="28" t="b">
+      <c r="C15" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -2605,7 +2529,7 @@
       <c r="B16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="28" t="b">
+      <c r="C16" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -2644,7 +2568,7 @@
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="28" t="b">
+      <c r="C17" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D17" s="3"/>
@@ -2681,7 +2605,7 @@
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="28" t="b">
+      <c r="C18" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -2722,7 +2646,7 @@
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="28" t="b">
+      <c r="C19" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -2761,7 +2685,7 @@
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="28" t="b">
+      <c r="C20" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -2802,7 +2726,7 @@
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="28" t="b">
+      <c r="C21" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -2843,7 +2767,7 @@
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="28" t="b">
+      <c r="C22" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -2884,7 +2808,7 @@
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="28" t="b">
+      <c r="C23" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -2925,7 +2849,7 @@
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="28" t="b">
+      <c r="C24" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D24" s="3"/>
@@ -2960,7 +2884,7 @@
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="28" t="b">
+      <c r="C25" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -3001,7 +2925,7 @@
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="28" t="b">
+      <c r="C26" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D26" s="3"/>
@@ -3036,7 +2960,7 @@
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="28" t="b">
+      <c r="C27" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -3075,7 +2999,7 @@
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="28" t="b">
+      <c r="C28" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -3116,7 +3040,7 @@
       <c r="B29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="28" t="b">
+      <c r="C29" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -3157,7 +3081,7 @@
       <c r="B30" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="28" t="b">
+      <c r="C30" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -3198,7 +3122,7 @@
       <c r="B31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="28" t="b">
+      <c r="C31" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -3237,7 +3161,7 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="28" t="b">
+      <c r="C32" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D32" s="3"/>
@@ -3272,7 +3196,7 @@
       <c r="B33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="28" t="b">
+      <c r="C33" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -3313,7 +3237,7 @@
       <c r="B34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="28" t="b">
+      <c r="C34" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -3352,7 +3276,7 @@
       <c r="B35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="28" t="b">
+      <c r="C35" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -3393,7 +3317,7 @@
       <c r="B36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="28" t="b">
+      <c r="C36" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -3432,7 +3356,7 @@
       <c r="B37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="28" t="b">
+      <c r="C37" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -3471,7 +3395,7 @@
       <c r="B38" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="28" t="b">
+      <c r="C38" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -3512,7 +3436,7 @@
       <c r="B39" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="28" t="b">
+      <c r="C39" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -3553,7 +3477,7 @@
       <c r="B40" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="28" t="b">
+      <c r="C40" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -3592,7 +3516,7 @@
       <c r="B41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="28" t="b">
+      <c r="C41" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D41" s="3" t="s">
@@ -3633,7 +3557,7 @@
       <c r="B42" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="28" t="b">
+      <c r="C42" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -3674,7 +3598,7 @@
       <c r="B43" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="28" t="b">
+      <c r="C43" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -3715,7 +3639,7 @@
       <c r="B44" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="28" t="b">
+      <c r="C44" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -3756,7 +3680,7 @@
       <c r="B45" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="28" t="b">
+      <c r="C45" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D45" s="3" t="s">
@@ -3797,7 +3721,7 @@
       <c r="B46" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="28" t="b">
+      <c r="C46" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -3838,7 +3762,7 @@
       <c r="B47" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="28" t="b">
+      <c r="C47" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -3877,7 +3801,7 @@
       <c r="B48" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="28" t="b">
+      <c r="C48" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -3916,7 +3840,7 @@
       <c r="B49" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="28" t="b">
+      <c r="C49" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -3955,7 +3879,7 @@
       <c r="B50" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="28" t="b">
+      <c r="C50" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -3994,7 +3918,7 @@
       <c r="B51" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="28" t="b">
+      <c r="C51" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D51" s="3"/>
@@ -4029,7 +3953,7 @@
       <c r="B52" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C52" s="28" t="b">
+      <c r="C52" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -4070,7 +3994,7 @@
       <c r="B53" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="28" t="b">
+      <c r="C53" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -4111,7 +4035,7 @@
       <c r="B54" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="28" t="b">
+      <c r="C54" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -4150,7 +4074,7 @@
       <c r="B55" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C55" s="28" t="b">
+      <c r="C55" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -4189,7 +4113,7 @@
         <v>67</v>
       </c>
       <c r="B56" s="3"/>
-      <c r="C56" s="28" t="b">
+      <c r="C56" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D56" s="3"/>
@@ -4224,7 +4148,7 @@
       <c r="B57" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C57" s="28" t="b">
+      <c r="C57" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -4263,7 +4187,7 @@
       <c r="B58" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="28" t="b">
+      <c r="C58" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -4302,7 +4226,7 @@
       <c r="B59" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C59" s="28" t="b">
+      <c r="C59" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -4343,7 +4267,7 @@
       <c r="B60" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C60" s="28" t="b">
+      <c r="C60" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -4384,7 +4308,7 @@
       <c r="B61" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C61" s="28" t="b">
+      <c r="C61" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -4423,7 +4347,7 @@
       <c r="B62" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C62" s="28" t="b">
+      <c r="C62" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D62" s="3"/>
@@ -4460,7 +4384,7 @@
       <c r="B63" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C63" s="28" t="b">
+      <c r="C63" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D63" s="3"/>
@@ -4495,7 +4419,7 @@
       <c r="B64" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C64" s="28" t="b">
+      <c r="C64" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D64" s="3"/>
@@ -4532,7 +4456,7 @@
       <c r="B65" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="28" t="b">
+      <c r="C65" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D65" s="3"/>
@@ -4569,7 +4493,7 @@
       <c r="B66" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C66" s="28" t="b">
+      <c r="C66" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -4610,7 +4534,7 @@
       <c r="B67" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C67" s="28" t="b">
+      <c r="C67" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D67" s="3"/>
@@ -4647,7 +4571,7 @@
       <c r="B68" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="28" t="b">
+      <c r="C68" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -4686,7 +4610,7 @@
       <c r="B69" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="28" t="b">
+      <c r="C69" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D69" s="3"/>
@@ -4723,7 +4647,7 @@
       <c r="B70" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C70" s="28" t="b">
+      <c r="C70" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -4764,7 +4688,7 @@
       <c r="B71" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C71" s="28" t="b">
+      <c r="C71" s="25" t="b">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -4803,7 +4727,7 @@
       <c r="B72" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C72" s="28" t="b">
+      <c r="C72" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -4844,7 +4768,7 @@
       <c r="B73" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C73" s="28" t="b">
+      <c r="C73" s="25" t="b">
         <v>1</v>
       </c>
       <c r="D73" s="3" t="s">
@@ -4885,7 +4809,7 @@
       <c r="B74" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C74" s="29" t="b">
+      <c r="C74" s="26" t="b">
         <v>0</v>
       </c>
       <c r="D74" s="12" t="s">
@@ -4926,7 +4850,7 @@
       <c r="B75" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="C75" s="29" t="b">
+      <c r="C75" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D75" s="12"/>
@@ -4961,7 +4885,7 @@
       <c r="B76" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="C76" s="29" t="b">
+      <c r="C76" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D76" s="12"/>
@@ -4996,7 +4920,7 @@
       <c r="B77" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="C77" s="29" t="b">
+      <c r="C77" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D77" s="12"/>
@@ -5031,7 +4955,7 @@
       <c r="B78" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="C78" s="29" t="b">
+      <c r="C78" s="26" t="b">
         <v>0</v>
       </c>
       <c r="D78" s="12"/>
@@ -5060,36 +4984,36 @@
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="26" t="s">
+      <c r="A79" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="B79" s="26" t="s">
+      <c r="B79" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C79" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="24"/>
-      <c r="E79" s="24"/>
-      <c r="F79" s="24"/>
-      <c r="G79" s="24"/>
-      <c r="H79" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="I79" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79" s="24">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M79" s="24">
+      <c r="C79" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" s="21">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M79" s="21">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
@@ -5101,7 +5025,7 @@
       <c r="B80" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C80" s="29" t="b">
+      <c r="C80" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D80" s="12"/>
@@ -5136,7 +5060,7 @@
       <c r="B81" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="29" t="b">
+      <c r="C81" s="26" t="b">
         <v>0</v>
       </c>
       <c r="D81" s="12"/>
@@ -5171,7 +5095,7 @@
       <c r="B82" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C82" s="29" t="b">
+      <c r="C82" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D82" s="12"/>
@@ -5206,7 +5130,7 @@
       <c r="B83" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="29" t="b">
+      <c r="C83" s="26" t="b">
         <v>1</v>
       </c>
       <c r="D83" s="12"/>
@@ -5241,7 +5165,7 @@
       <c r="B84" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C84" s="29" t="b">
+      <c r="C84" s="26" t="b">
         <v>0</v>
       </c>
       <c r="D84" s="12"/>
@@ -5884,18 +5808,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -5936,16 +5860,16 @@
       <c r="B3" s="19">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
     </row>
     <row r="4" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
@@ -6081,18 +6005,18 @@
       <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -6102,16 +6026,16 @@
       <c r="B9" s="19">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.25">
@@ -6234,26 +6158,36 @@
       <c r="J13" s="14"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>46172</v>
       </c>
       <c r="B14" s="19">
         <v>0.625</v>
       </c>
-      <c r="C14" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="37"/>
+      <c r="C14" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <v>46172</v>
       </c>
@@ -6261,29 +6195,33 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>209</v>
+        <v>109</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
+        <v>111</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>113</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>46172</v>
       </c>
@@ -6291,33 +6229,33 @@
         <v>0.6875</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>212</v>
+        <v>127</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>46172</v>
       </c>
@@ -6325,33 +6263,33 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <v>46172</v>
       </c>
@@ -6359,33 +6297,25 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>162</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>46172</v>
       </c>
@@ -6393,25 +6323,33 @@
         <v>0.75</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
+        <v>166</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>138</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <v>46172</v>
       </c>
@@ -6419,33 +6357,25 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>138</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <v>46172</v>
       </c>
@@ -6453,16 +6383,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
@@ -6471,7 +6401,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>46172</v>
       </c>
@@ -6479,17 +6409,13 @@
         <v>0.8125</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>140</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
@@ -6497,7 +6423,7 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <v>46172</v>
       </c>
@@ -6505,10 +6431,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
@@ -6519,64 +6445,37 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>46172</v>
       </c>
       <c r="B24" s="19">
         <v>0.85416666666666663</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
+      <c r="C24" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
-        <v>46172</v>
-      </c>
-      <c r="B25" s="19">
-        <v>0.875</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B26"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -6586,7 +6485,7 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -6596,7 +6495,7 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -6606,7 +6505,7 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -6616,7 +6515,7 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -6626,7 +6525,7 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -6637,16 +6536,15 @@
       <c r="J32" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="C3:J3"/>
     <mergeCell ref="C9:J9"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="C24:J24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:J7 C9:J11 D12:J12 C12:C14 D13:G13 C15:H15 C16:J17 G18:J18 C18:F19 C20:J24">
+  <conditionalFormatting sqref="C4:J7 C9:J11 D12:J12 C12:C13 D13:G13 C14:H14 C15:J16 G17:J17 C17:F18 C19:J23">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="5th">
       <formula>NOT(ISERROR(SEARCH("5th",C4)))</formula>
     </cfRule>

--- a/Entry List 10_40am.xlsx
+++ b/Entry List 10_40am.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B75157-38CD-495C-94F3-566E5435B311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46639DD3-B9C1-4A4A-B62F-3992C6359389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
   </bookViews>
@@ -6192,7 +6192,7 @@
         <v>46172</v>
       </c>
       <c r="B15" s="19">
-        <v>0.66666666666666663</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>212</v>
@@ -6226,7 +6226,7 @@
         <v>46172</v>
       </c>
       <c r="B16" s="19">
-        <v>0.6875</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>127</v>
@@ -6260,7 +6260,7 @@
         <v>46172</v>
       </c>
       <c r="B17" s="19">
-        <v>0.70833333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>155</v>
@@ -6294,7 +6294,7 @@
         <v>46172</v>
       </c>
       <c r="B18" s="19">
-        <v>0.72916666666666663</v>
+        <v>0.70833333333333304</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>117</v>
@@ -6320,7 +6320,7 @@
         <v>46172</v>
       </c>
       <c r="B19" s="19">
-        <v>0.75</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>163</v>
@@ -6354,7 +6354,7 @@
         <v>46172</v>
       </c>
       <c r="B20" s="19">
-        <v>0.77083333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>144</v>
@@ -6380,7 +6380,7 @@
         <v>46172</v>
       </c>
       <c r="B21" s="19">
-        <v>0.79166666666666663</v>
+        <v>0.77083333333333404</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>167</v>
@@ -6406,7 +6406,7 @@
         <v>46172</v>
       </c>
       <c r="B22" s="19">
-        <v>0.8125</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>146</v>
@@ -6428,7 +6428,7 @@
         <v>46172</v>
       </c>
       <c r="B23" s="19">
-        <v>0.83333333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>169</v>
@@ -6450,7 +6450,7 @@
         <v>46172</v>
       </c>
       <c r="B24" s="19">
-        <v>0.85416666666666663</v>
+        <v>0.83333333333333404</v>
       </c>
       <c r="C24" s="31" t="s">
         <v>170</v>

--- a/Entry List 10_40am.xlsx
+++ b/Entry List 10_40am.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46639DD3-B9C1-4A4A-B62F-3992C6359389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C7BB91-FEFB-4276-85A0-7C75B9BF49A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
+    <workbookView xWindow="1275" yWindow="1035" windowWidth="20370" windowHeight="10905" firstSheet="2" activeTab="2" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="213">
   <si>
     <t>Le Roux Strydom</t>
   </si>
@@ -680,9 +680,6 @@
     <t>2nd &amp; Below Group 9</t>
   </si>
   <si>
-    <t>2nd &amp; Below Group 10</t>
-  </si>
-  <si>
     <t>5th &amp; Below Round 32 Match 1</t>
   </si>
   <si>
@@ -693,12 +690,6 @@
   </si>
   <si>
     <t>2nd &amp; Below Round 32 Match 2</t>
-  </si>
-  <si>
-    <t>2nd &amp; Below Round 32 Match 3</t>
-  </si>
-  <si>
-    <t>2nd &amp; Below Round 32 Match 4</t>
   </si>
   <si>
     <t>5th &amp; Below Round 16 Match1</t>
@@ -1937,7 +1928,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>82</v>
@@ -5809,7 +5800,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -6006,7 +5997,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="29"/>
@@ -6052,22 +6043,22 @@
         <v>99</v>
       </c>
       <c r="E10" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="G10" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="H10" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="I10" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="J10" s="17" t="s">
         <v>126</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="45" x14ac:dyDescent="0.25">
@@ -6077,27 +6068,26 @@
       <c r="B11" s="19">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="D11" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17" t="s">
+      <c r="F11" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="G11" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="H11" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="I11" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="J11" s="17" t="s">
         <v>126</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -6152,7 +6142,9 @@
       <c r="F13" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="G13" s="17"/>
+      <c r="G13" s="17" t="s">
+        <v>143</v>
+      </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
@@ -6166,23 +6158,19 @@
         <v>0.625</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="E14" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="F14" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="F14" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>211</v>
-      </c>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
       <c r="K14" s="1"/>
@@ -6195,7 +6183,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>107</v>
@@ -6544,7 +6532,7 @@
     <mergeCell ref="C24:J24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:J7 C9:J11 D12:J12 C12:C13 D13:G13 C14:H14 C15:J16 G17:J17 C17:F18 C19:J23">
+  <conditionalFormatting sqref="C4:J7 D12:J12 C12:C13 D13:G13 C14:H14 C15:J16 G17:J17 C17:F18 C19:J23 C9:J9 F10:J11 C10:E10 D11:E11">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="5th">
       <formula>NOT(ISERROR(SEARCH("5th",C4)))</formula>
     </cfRule>

--- a/Entry List 10_40am.xlsx
+++ b/Entry List 10_40am.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C7BB91-FEFB-4276-85A0-7C75B9BF49A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B3BFA6-F9A8-4377-8415-A1FC03EDDADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="1035" windowWidth="20370" windowHeight="10905" firstSheet="2" activeTab="2" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{264A1161-47FB-460F-8362-5F7BA003EA4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="212">
   <si>
     <t>Le Roux Strydom</t>
   </si>
@@ -251,9 +251,6 @@
     <t xml:space="preserve">Boundary </t>
   </si>
   <si>
-    <t>Tamika Van Aa</t>
-  </si>
-  <si>
     <t>Boundary</t>
   </si>
   <si>
@@ -323,15 +320,9 @@
     <t>Maties Rank</t>
   </si>
   <si>
-    <t>Ezra Msindeni</t>
-  </si>
-  <si>
     <t>Shane Overmayer</t>
   </si>
   <si>
-    <t>Demos Dracoulides</t>
-  </si>
-  <si>
     <t>Denver Sweatz</t>
   </si>
   <si>
@@ -590,9 +581,6 @@
     <t>Tashreeq Samodien</t>
   </si>
   <si>
-    <t>Kirk Daries</t>
-  </si>
-  <si>
     <t>Gentlmen's Group 9</t>
   </si>
   <si>
@@ -702,6 +690,15 @@
   </si>
   <si>
     <t>Paid</t>
+  </si>
+  <si>
+    <t>paid or not</t>
+  </si>
+  <si>
+    <t>Kamiel Ebrahim</t>
+  </si>
+  <si>
+    <t>Mother City</t>
   </si>
 </sst>
 </file>
@@ -874,16 +871,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -953,12 +947,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{874BD9BD-1606-40B6-95A9-D06C7CFE4EDB}"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="35">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1020,6 +1029,237 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="medium">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="medium">
           <color auto="1"/>
@@ -1059,22 +1299,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
@@ -1095,22 +1319,6 @@
         <horizontal style="thin">
           <color auto="1"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1136,7 +1344,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
         </left>
@@ -1146,9 +1354,15 @@
         <top style="thin">
           <color auto="1"/>
         </top>
-        <bottom style="medium">
+        <bottom style="thin">
           <color auto="1"/>
         </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1174,7 +1388,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
         </left>
@@ -1184,9 +1398,15 @@
         <top style="thin">
           <color auto="1"/>
         </top>
-        <bottom style="medium">
+        <bottom style="thin">
           <color auto="1"/>
         </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1212,7 +1432,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
         </left>
@@ -1222,9 +1442,15 @@
         <top style="thin">
           <color auto="1"/>
         </top>
-        <bottom style="medium">
+        <bottom style="thin">
           <color auto="1"/>
         </bottom>
+        <vertical style="medium">
+          <color auto="1"/>
+        </vertical>
+        <horizontal style="thin">
+          <color auto="1"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1250,7 +1476,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
         </left>
@@ -1260,22 +1486,6 @@
         <top style="thin">
           <color auto="1"/>
         </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
@@ -1285,136 +1495,6 @@
         <horizontal style="thin">
           <color auto="1"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="medium">
-          <color auto="1"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1437,7 +1517,7 @@
       </extLst>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
         </left>
@@ -1447,22 +1527,6 @@
         <top style="thin">
           <color auto="1"/>
         </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
@@ -1472,22 +1536,6 @@
         <horizontal style="thin">
           <color auto="1"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="medium">
-          <color auto="1"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1551,34 +1599,38 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB2F57D0-72E5-447F-A3B0-45114F2DF106}" name="Table1" displayName="Table1" ref="A1:M85" totalsRowCount="1" headerRowDxfId="32">
-  <autoFilter ref="A1:M84" xr:uid="{CB2F57D0-72E5-447F-A3B0-45114F2DF106}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{2E76C30E-1712-40BE-9549-71C9C93B502D}" name="Name" totalsRowLabel="Total" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{B49483E4-5D8F-40B6-8641-DD9E65DC8898}" name="Club" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{059F9E1A-99DD-4E87-BCC2-21ED7DCBC75C}" name="Paid" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{6D81A917-4325-4EEA-A94E-463FBA3CD2DE}" name="Registered League" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{77DB4597-4DE2-49A3-8551-3945B9C26A0F}" name="Current League Rank" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{28EE5F78-650B-40EA-9D3E-86070DEB6E33}" name="SATTB Rank" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{B0512E74-2097-4749-8D71-028F16552145}" name="Maties Rank" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{33263E04-7CFE-40B1-A063-335CFE82FBBA}" name="2nd &amp; Below" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB2F57D0-72E5-447F-A3B0-45114F2DF106}" name="Table1" displayName="Table1" ref="A1:N82" totalsRowCount="1" headerRowDxfId="34">
+  <autoFilter ref="A1:N81" xr:uid="{CB2F57D0-72E5-447F-A3B0-45114F2DF106}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{2E76C30E-1712-40BE-9549-71C9C93B502D}" name="Name" totalsRowLabel="Total" dataDxfId="33" totalsRowDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{B49483E4-5D8F-40B6-8641-DD9E65DC8898}" name="Club" dataDxfId="32" totalsRowDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{059F9E1A-99DD-4E87-BCC2-21ED7DCBC75C}" name="Paid" dataDxfId="31" totalsRowDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{6D81A917-4325-4EEA-A94E-463FBA3CD2DE}" name="Registered League" dataDxfId="30" totalsRowDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{77DB4597-4DE2-49A3-8551-3945B9C26A0F}" name="Current League Rank" dataDxfId="29" totalsRowDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{28EE5F78-650B-40EA-9D3E-86070DEB6E33}" name="SATTB Rank" dataDxfId="28" totalsRowDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{B0512E74-2097-4749-8D71-028F16552145}" name="Maties Rank" dataDxfId="27" totalsRowDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{33263E04-7CFE-40B1-A063-335CFE82FBBA}" name="2nd &amp; Below" totalsRowFunction="custom" dataDxfId="26" totalsRowDxfId="13">
       <totalsRowFormula>COUNTIF(Table1[2nd &amp; Below],TRUE)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0F990E8B-E4C9-4D0D-9CC5-A6D55E12654F}" name="5th &amp; Below" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="14">
+    <tableColumn id="5" xr3:uid="{0F990E8B-E4C9-4D0D-9CC5-A6D55E12654F}" name="5th &amp; Below" totalsRowFunction="custom" dataDxfId="25" totalsRowDxfId="12">
       <totalsRowFormula>COUNTIF(Table1[5th &amp; Below],TRUE)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E3251279-4988-46EB-AD20-00F1E80654F1}" name="Senior Women" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="6" xr3:uid="{E3251279-4988-46EB-AD20-00F1E80654F1}" name="Senior Women" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="11">
       <totalsRowFormula>COUNTIF(Table1[Senior Women],TRUE)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D79D3630-5FB1-4D9E-A424-AC37ECA2C0CD}" name="Senior Men" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="10">
+    <tableColumn id="7" xr3:uid="{D79D3630-5FB1-4D9E-A424-AC37ECA2C0CD}" name="Senior Men" totalsRowFunction="custom" dataDxfId="23" totalsRowDxfId="10">
       <totalsRowFormula>COUNTIF(Table1[Senior Men],TRUE)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{AC7ED2C1-E830-49D6-B996-8C9D9B21457E}" name="Column1" dataDxfId="9" totalsRowDxfId="8">
+    <tableColumn id="11" xr3:uid="{AC7ED2C1-E830-49D6-B996-8C9D9B21457E}" name="Column1" dataDxfId="22" totalsRowDxfId="9">
       <calculatedColumnFormula>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{524892D6-ACD8-434C-B13E-1FC70A4B293F}" name="Column2" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6">
+    <tableColumn id="12" xr3:uid="{524892D6-ACD8-434C-B13E-1FC70A4B293F}" name="Column2" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="8">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Column1]]=1,120,180)</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table1[Column2])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{5CCB6B96-BC6A-4A61-A2FC-0E19B78BDF02}" name="paid or not" totalsRowFunction="custom" dataDxfId="6" totalsRowDxfId="7">
+      <calculatedColumnFormula>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</calculatedColumnFormula>
+      <totalsRowFormula>SUM(Table1[paid or not])</totalsRowFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1905,7 +1957,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -1917,10 +1969,10 @@
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
     <col min="10" max="10" width="16.42578125" customWidth="1"/>
     <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="13" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1928,19 +1980,19 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -1955,20 +2007,23 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="24" t="b">
+      <c r="C2" s="23" t="b">
         <v>1</v>
       </c>
       <c r="D2" s="2"/>
@@ -1977,51 +2032,55 @@
         <v>266</v>
       </c>
       <c r="G2" s="2"/>
-      <c r="H2" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="11">
+      <c r="H2" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="10">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
         <v>2</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="10">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="25" t="b">
+      <c r="C3" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7" t="b">
+      <c r="H3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L3" s="3">
@@ -2032,15 +2091,19 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="25" t="b">
+      <c r="C4" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D4" s="3"/>
@@ -2049,16 +2112,16 @@
         <v>110</v>
       </c>
       <c r="G4" s="3"/>
-      <c r="H4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7" t="b">
+      <c r="H4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="3">
@@ -2069,19 +2132,23 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="N4" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="25" t="b">
+      <c r="C5" s="33" t="b">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E5" s="3">
         <v>2</v>
@@ -2090,16 +2157,16 @@
         <v>24</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7" t="b">
+      <c r="H5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L5" s="3">
@@ -2110,15 +2177,19 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="N5" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="25" t="b">
+      <c r="C6" s="33" t="b">
         <v>0</v>
       </c>
       <c r="D6" s="3"/>
@@ -2127,16 +2198,16 @@
         <v>2</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="7" t="b">
+      <c r="H6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="3">
@@ -2147,19 +2218,23 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="N6" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="25" t="b">
+      <c r="C7" s="33" t="b">
         <v>0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E7" s="3">
         <v>15</v>
@@ -2168,16 +2243,16 @@
         <v>150</v>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="7" t="b">
+      <c r="H7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L7" s="3">
@@ -2188,19 +2263,23 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="N7" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="25" t="b">
+      <c r="C8" s="33" t="b">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E8" s="3">
         <v>18</v>
@@ -2209,16 +2288,16 @@
         <v>14</v>
       </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7" t="b">
+      <c r="H8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="3">
@@ -2229,19 +2308,23 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="N8" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="25" t="b">
+      <c r="C9" s="33" t="b">
         <v>0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E9" s="3">
         <v>23</v>
@@ -2250,16 +2333,16 @@
         <v>47</v>
       </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="7" t="b">
+      <c r="H9" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="3">
@@ -2270,19 +2353,23 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="N9" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="25" t="b">
+      <c r="C10" s="33" t="b">
         <v>0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E10" s="3">
         <v>22</v>
@@ -2291,16 +2378,16 @@
         <v>7</v>
       </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="7" t="b">
+      <c r="H10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="3">
@@ -2311,19 +2398,23 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="N10" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="25" t="b">
+      <c r="C11" s="33" t="b">
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E11" s="3">
         <v>3</v>
@@ -2332,16 +2423,16 @@
         <v>4</v>
       </c>
       <c r="G11" s="3"/>
-      <c r="H11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="7" t="b">
+      <c r="H11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="3">
@@ -2352,19 +2443,23 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="25" t="b">
+      <c r="C12" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E12" s="3">
         <v>15</v>
@@ -2373,16 +2468,16 @@
         <v>176</v>
       </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="7" t="b">
+      <c r="H12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="3">
@@ -2393,19 +2488,23 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N12" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="25" t="b">
+      <c r="C13" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E13" s="3">
         <v>24</v>
@@ -2414,16 +2513,16 @@
         <v>161</v>
       </c>
       <c r="G13" s="3"/>
-      <c r="H13" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="7" t="b">
+      <c r="H13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L13" s="3">
@@ -2434,35 +2533,39 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N13" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="25" t="b">
+      <c r="C14" s="24" t="b">
         <v>0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E14" s="3">
         <v>28</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="7" t="b">
+      <c r="H14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L14" s="3">
@@ -2473,35 +2576,39 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N14" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="25" t="b">
+      <c r="C15" s="24" t="b">
         <v>0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E15" s="3">
         <v>7</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" s="7" t="b">
+      <c r="H15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="3">
@@ -2512,113 +2619,125 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N15" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E16" s="3">
-        <v>8</v>
-      </c>
-      <c r="F16" s="3"/>
+      <c r="C16" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3">
+        <v>199</v>
+      </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="7" t="b">
-        <v>0</v>
+      <c r="H16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="L16" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="N16" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="C17" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E17" s="3">
+        <v>15</v>
+      </c>
       <c r="F17" s="3">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="7" t="b">
+      <c r="H17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L17" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N17" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="25" t="b">
+      <c r="C18" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E18" s="3">
-        <v>15</v>
-      </c>
-      <c r="F18" s="3">
-        <v>162</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" s="7" t="b">
+      <c r="H18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="3">
@@ -2629,76 +2748,86 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N18" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="25" t="b">
+      <c r="C19" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="3">
+        <v>7</v>
+      </c>
+      <c r="F19" s="3">
+        <v>221</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>2</v>
+      </c>
+      <c r="M19" s="3">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-      <c r="E19" s="3">
-        <v>13</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M19" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N19" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="25" t="b">
+      <c r="C20" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E20" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" s="3">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" s="7" t="b">
+      <c r="H20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="3">
@@ -2709,37 +2838,41 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N20" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="25" t="b">
+      <c r="C21" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E21" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F21" s="3">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" s="7" t="b">
+      <c r="H21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L21" s="3">
@@ -2750,189 +2883,207 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N21" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="25" t="b">
+      <c r="C22" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E22" s="3">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
+        <v>544</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
         <v>2</v>
       </c>
-      <c r="F22" s="3">
-        <v>224</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
-      </c>
       <c r="M22" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N22" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E23" s="3">
-        <v>3</v>
-      </c>
-      <c r="F23" s="3">
-        <v>544</v>
-      </c>
+      <c r="C23" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" s="7" t="b">
-        <v>1</v>
+      <c r="H23" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="L23" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N23" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="C24" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E24" s="3">
+        <v>19</v>
+      </c>
+      <c r="F24" s="3">
+        <v>331</v>
+      </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" s="7" t="b">
-        <v>0</v>
+      <c r="H24" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="L24" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="N24" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E25" s="3">
-        <v>19</v>
-      </c>
-      <c r="F25" s="3">
-        <v>331</v>
-      </c>
+      <c r="C25" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" s="7" t="b">
-        <v>1</v>
+      <c r="H25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="L25" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N25" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="C26" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E26" s="3">
+        <v>38</v>
+      </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" s="7" t="b">
+      <c r="H26" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="3">
@@ -2943,118 +3094,132 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N26" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="25" t="b">
+      <c r="C27" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E27" s="3">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F27" s="3">
+        <v>146</v>
+      </c>
       <c r="G27" s="3"/>
-      <c r="H27" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" s="7" t="b">
-        <v>0</v>
+      <c r="H27" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="L27" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="N27" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="25" t="b">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="C28" s="24" t="b">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E28" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28" s="3">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="G28" s="3"/>
-      <c r="H28" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I28" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" s="7" t="b">
+      <c r="H28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N28" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="25" t="b">
+      <c r="C29" s="24" t="b">
         <v>0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E29" s="3">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F29" s="3">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="G29" s="3"/>
-      <c r="H29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" s="7" t="b">
-        <v>1</v>
+      <c r="H29" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="L29" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
@@ -3064,76 +3229,78 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N29" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="25" t="b">
+      <c r="C30" s="24" t="b">
         <v>0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E30" s="3">
-        <v>37</v>
-      </c>
-      <c r="F30" s="3">
-        <v>141</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I30" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" s="7" t="b">
+      <c r="H30" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L30" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="N30" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E31" s="3">
-        <v>34</v>
-      </c>
+      <c r="C31" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I31" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" s="7" t="b">
+      <c r="H31" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="3">
@@ -3144,31 +3311,41 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N31" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="C32" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
+        <v>179</v>
+      </c>
       <c r="G32" s="3"/>
-      <c r="H32" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I32" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" s="7" t="b">
+      <c r="H32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L32" s="3">
@@ -3179,37 +3356,39 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N32" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="25" t="b">
+      <c r="C33" s="24" t="b">
         <v>0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E33" s="3">
-        <v>8</v>
-      </c>
-      <c r="F33" s="3">
-        <v>179</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I33" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" s="7" t="b">
+      <c r="H33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="3">
@@ -3220,35 +3399,41 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N33" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="25" t="b">
-        <v>0</v>
+      <c r="C34" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E34" s="3">
-        <v>25</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="F34" s="3">
+        <v>46</v>
+      </c>
       <c r="G34" s="3"/>
-      <c r="H34" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" s="7" t="b">
+      <c r="H34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="3">
@@ -3259,156 +3444,172 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N34" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="25" t="b">
-        <v>1</v>
+      <c r="C35" s="24" t="b">
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E35" s="3">
-        <v>22</v>
-      </c>
-      <c r="F35" s="3">
-        <v>46</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I35" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" s="7" t="b">
+      <c r="H35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N35" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="25" t="b">
+      <c r="C36" s="24" t="b">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E36" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I36" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" s="7" t="b">
-        <v>0</v>
+      <c r="H36" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="L36" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="N36" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="25" t="b">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="C37" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E37" s="3">
         <v>5</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3">
+        <v>71</v>
+      </c>
       <c r="G37" s="3"/>
-      <c r="H37" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I37" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" s="7" t="b">
+      <c r="H37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L37" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N37" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="25" t="b">
+      <c r="C38" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E38" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" s="7" t="b">
+      <c r="H38" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L38" s="3">
@@ -3419,76 +3620,84 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N38" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="25" t="b">
+      <c r="C39" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E39" s="3">
-        <v>10</v>
-      </c>
-      <c r="F39" s="3">
-        <v>36</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" s="7" t="b">
-        <v>1</v>
+      <c r="H39" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="L39" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="N39" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="25" t="b">
+      <c r="C40" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E40" s="3">
-        <v>24</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="F40" s="3">
+        <v>766</v>
+      </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I40" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" s="7" t="b">
+      <c r="H40" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L40" s="3">
@@ -3499,78 +3708,86 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N40" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="25" t="b">
+      <c r="C41" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E41" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F41" s="3">
-        <v>766</v>
+        <v>749</v>
       </c>
       <c r="G41" s="3"/>
-      <c r="H41" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I41" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J41" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" s="7" t="b">
+      <c r="H41" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L41" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N41" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="25" t="b">
+      <c r="C42" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E42" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F42" s="3">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="G42" s="3"/>
-      <c r="H42" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" s="7" t="b">
+      <c r="H42" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L42" s="3">
@@ -3581,160 +3798,174 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N42" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="25" t="b">
+      <c r="C43" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E43" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F43" s="3">
-        <v>744</v>
+        <v>321</v>
       </c>
       <c r="G43" s="3"/>
-      <c r="H43" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I43" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" s="7" t="b">
+      <c r="H43" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L43" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="N43" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="25" t="b">
+      <c r="C44" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>182</v>
       </c>
       <c r="E44" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3">
-        <v>321</v>
+        <v>388</v>
       </c>
       <c r="G44" s="3"/>
-      <c r="H44" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I44" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" s="7" t="b">
+      <c r="H44" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L44" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M44" s="3">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N44" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3">
+        <v>427</v>
+      </c>
+      <c r="G45" s="3"/>
+      <c r="H45" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" s="3">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
         <v>2</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M45" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E45" s="3">
-        <v>10</v>
-      </c>
-      <c r="F45" s="3">
-        <v>388</v>
-      </c>
-      <c r="G45" s="3"/>
-      <c r="H45" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M45" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="N45" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="25" t="b">
-        <v>1</v>
+      <c r="C46" s="33" t="b">
+        <v>0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E46" s="3">
-        <v>1</v>
-      </c>
-      <c r="F46" s="3">
-        <v>427</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" s="7" t="b">
+      <c r="H46" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L46" s="3">
@@ -3745,35 +3976,39 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="3" t="s">
+      <c r="N46" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C47" s="25" t="b">
-        <v>1</v>
+      <c r="C47" s="33" t="b">
+        <v>0</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E47" s="3">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" s="7" t="b">
+      <c r="H47" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L47" s="3">
@@ -3784,35 +4019,39 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="3" t="s">
+      <c r="N47" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="25" t="b">
-        <v>1</v>
+      <c r="C48" s="33" t="b">
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E48" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" s="7" t="b">
+      <c r="H48" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L48" s="3">
@@ -3823,36 +4062,40 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="N48" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="25" t="b">
-        <v>1</v>
+      <c r="C49" s="33" t="b">
+        <v>0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E49" s="3">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" s="7" t="b">
-        <v>1</v>
+      <c r="H49" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
@@ -3862,36 +4105,36 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B50" s="3" t="s">
+      <c r="N49" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E50" s="3">
-        <v>19</v>
-      </c>
+      <c r="C50" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K50" s="7" t="b">
-        <v>0</v>
+      <c r="H50" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="L50" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
@@ -3901,32 +4144,42 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N50" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+        <v>61</v>
+      </c>
+      <c r="C51" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E51" s="3">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3">
+        <v>1</v>
+      </c>
       <c r="G51" s="3"/>
-      <c r="H51" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" s="7" t="b">
-        <v>1</v>
+      <c r="H51" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="L51" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
@@ -3936,117 +4189,121 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N51" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="25" t="b">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="C52" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E52" s="3">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I52" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K52" s="7" t="b">
+      <c r="H52" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L52" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N52" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C53" s="25" t="b">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="C53" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E53" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F53" s="3">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G53" s="3"/>
-      <c r="H53" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I53" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K53" s="7" t="b">
-        <v>0</v>
+      <c r="H53" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="L53" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N53" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C54" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E54" s="3">
-        <v>29</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I54" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J54" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" s="7" t="b">
+      <c r="H54" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L54" s="3">
@@ -4057,37 +4314,39 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N54" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" s="25" t="b">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="C55" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E55" s="3">
-        <v>8</v>
-      </c>
-      <c r="F55" s="3">
-        <v>38</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F55" s="3"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" s="7" t="b">
+      <c r="H55" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="b">
         <v>1</v>
       </c>
       <c r="L55" s="3">
@@ -4098,69 +4357,85 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N55" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E56" s="3">
+        <v>13</v>
+      </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I56" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" s="7" t="b">
+      <c r="H56" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K56" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L56" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M56" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="N56" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" s="25" t="b">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="C57" s="24" t="b">
+        <v>1</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E57" s="3">
-        <v>30</v>
-      </c>
-      <c r="F57" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="F57" s="3">
+        <v>331</v>
+      </c>
       <c r="G57" s="3"/>
-      <c r="H57" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" s="7" t="b">
-        <v>1</v>
+      <c r="H57" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="L57" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
@@ -4170,76 +4445,84 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N57" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C58" s="25" t="b">
+        <v>78</v>
+      </c>
+      <c r="C58" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E58" s="3">
-        <v>13</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="F58" s="3">
+        <v>335</v>
+      </c>
       <c r="G58" s="3"/>
-      <c r="H58" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K58" s="7" t="b">
+      <c r="H58" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="3">
         <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M58" s="3">
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="N58" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C59" s="25" t="b">
+        <v>78</v>
+      </c>
+      <c r="C59" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E59" s="3">
-        <v>16</v>
-      </c>
-      <c r="F59" s="3">
-        <v>331</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F59" s="3"/>
       <c r="G59" s="3"/>
-      <c r="H59" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" s="7" t="b">
+      <c r="H59" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L59" s="3">
@@ -4250,37 +4533,37 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N59" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C60" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E60" s="3">
-        <v>40</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C60" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
       <c r="F60" s="3">
-        <v>335</v>
+        <v>27</v>
       </c>
       <c r="G60" s="3"/>
-      <c r="H60" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" s="7" t="b">
+      <c r="H60" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="3">
@@ -4291,35 +4574,35 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N60" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E61" s="3">
-        <v>22</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C61" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
-      <c r="H61" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" s="7" t="b">
+      <c r="H61" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L61" s="3">
@@ -4330,33 +4613,37 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N61" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C62" s="25" t="b">
+        <v>78</v>
+      </c>
+      <c r="C62" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G62" s="3"/>
-      <c r="H62" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" s="7" t="b">
+      <c r="H62" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="3">
@@ -4367,31 +4654,37 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N62" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C63" s="25" t="b">
+        <v>78</v>
+      </c>
+      <c r="C63" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
+      <c r="F63" s="3">
+        <v>344</v>
+      </c>
       <c r="G63" s="3"/>
-      <c r="H63" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I63" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" s="7" t="b">
+      <c r="H63" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="3">
@@ -4402,70 +4695,82 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N63" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C64" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E64" s="3">
+        <v>14</v>
+      </c>
+      <c r="F64" s="3">
+        <v>37</v>
+      </c>
+      <c r="G64" s="3"/>
+      <c r="H64" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L64" s="3">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M64" s="3">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N64" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C64" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3">
-        <v>19</v>
-      </c>
-      <c r="G64" s="3"/>
-      <c r="H64" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I64" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L64" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M64" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="B65" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C65" s="25" t="b">
+        <v>78</v>
+      </c>
+      <c r="C65" s="24" t="b">
         <v>1</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3">
-        <v>344</v>
+        <v>137</v>
       </c>
       <c r="G65" s="3"/>
-      <c r="H65" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I65" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" s="7" t="b">
+      <c r="H65" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" s="6" t="b">
         <v>0</v>
       </c>
       <c r="L65" s="3">
@@ -4476,763 +4781,706 @@
         <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N65" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3">
+        <v>2</v>
+      </c>
+      <c r="G66" s="3"/>
+      <c r="H66" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" s="3">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M66" s="3">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N66" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E67" s="3">
+        <v>27</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" s="3">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M67" s="3">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N67" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D66" s="3" t="s">
+      <c r="C68" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E68" s="3">
+        <v>7</v>
+      </c>
+      <c r="F68" s="3">
+        <v>69</v>
+      </c>
+      <c r="G68" s="3"/>
+      <c r="H68" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" s="3">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M68" s="3">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N68" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C69" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E69" s="3">
+        <v>7</v>
+      </c>
+      <c r="F69" s="3">
+        <v>23</v>
+      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" s="3">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M69" s="3">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N69" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E70" s="11">
+        <v>32</v>
+      </c>
+      <c r="F70" s="11">
+        <v>701</v>
+      </c>
+      <c r="G70" s="11"/>
+      <c r="H70" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I70" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>2</v>
+      </c>
+      <c r="M70" s="3">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
         <v>180</v>
       </c>
-      <c r="E66" s="3">
-        <v>14</v>
-      </c>
-      <c r="F66" s="3">
-        <v>37</v>
-      </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L66" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M66" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+      <c r="N70" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C71" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I71" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" s="11">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M71" s="11">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N71" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C72" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I72" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" s="11">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M72" s="11">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N72" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C73" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I73" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" s="11">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M73" s="11">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N73" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C74" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I74" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" s="11">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>2</v>
+      </c>
+      <c r="M74" s="11">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>180</v>
+      </c>
+      <c r="N74" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C75" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I75" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" s="20">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M75" s="20">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N75" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="C76" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" s="21"/>
+      <c r="J76" s="21"/>
+      <c r="K76" s="21"/>
+      <c r="L76" s="20">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M76" s="20">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N76" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" s="11">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>2</v>
+      </c>
+      <c r="M77" s="11">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>180</v>
+      </c>
+      <c r="N77" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" s="11">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M78" s="11">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N78" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79" s="11">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M79" s="11">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N79" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" s="11">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M80" s="11">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N80" s="3">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81" s="11">
+        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="M81" s="11">
+        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
+        <v>120</v>
+      </c>
+      <c r="N81" s="11">
+        <f>IF(Table1[[#This Row],[Paid]],Table1[[#This Row],[Column2]],0)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C67" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3">
-        <v>137</v>
-      </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I67" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M67" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C68" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E68" s="3">
-        <v>20</v>
-      </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I68" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J68" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L68" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M68" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C69" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3">
-        <v>2</v>
-      </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L69" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M69" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C70" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3">
-        <v>411</v>
-      </c>
-      <c r="G70" s="3"/>
-      <c r="H70" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I70" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L70" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M70" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C71" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E71" s="3">
-        <v>27</v>
-      </c>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I71" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M71" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C72" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E72" s="3">
-        <v>7</v>
-      </c>
-      <c r="F72" s="3">
-        <v>69</v>
-      </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I72" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J72" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L72" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M72" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C73" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E73" s="3">
-        <v>7</v>
-      </c>
-      <c r="F73" s="3">
-        <v>23</v>
-      </c>
-      <c r="G73" s="3"/>
-      <c r="H73" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I73" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L73" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M73" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C74" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="E74" s="12">
-        <v>32</v>
-      </c>
-      <c r="F74" s="12">
-        <v>701</v>
-      </c>
-      <c r="G74" s="12"/>
-      <c r="H74" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I74" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74" s="3">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
-      </c>
-      <c r="M74" s="3">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C75" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I75" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" s="12">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M75" s="12">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C76" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I76" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" s="12">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M76" s="12">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C77" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I77" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L77" s="12">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M77" s="12">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C78" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L78" s="12">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M78" s="12">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="B79" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="C79" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I79" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79" s="21">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M79" s="21">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I80" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L80" s="12">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>2</v>
-      </c>
-      <c r="M80" s="12">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>180</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I81" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J81" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L81" s="12">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M81" s="12">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C82" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I82" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L82" s="12">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M82" s="12">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I83" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L83" s="12">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M83" s="12">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C84" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I84" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L84" s="12">
-        <f>COUNTIF(Table1[[#This Row],[2nd &amp; Below]:[Senior Men]],TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="M84" s="12">
-        <f>IF(Table1[[#This Row],[Column1]]=1,120,180)</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="5"/>
-      <c r="H85" s="5">
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4">
         <f>COUNTIF(Table1[2nd &amp; Below],TRUE)</f>
         <v>37</v>
       </c>
-      <c r="I85" s="5">
+      <c r="I82" s="4">
         <f>COUNTIF(Table1[5th &amp; Below],TRUE)</f>
         <v>33</v>
       </c>
-      <c r="J85" s="5">
+      <c r="J82" s="4">
         <f>COUNTIF(Table1[Senior Women],TRUE)</f>
-        <v>7</v>
-      </c>
-      <c r="K85" s="5">
+        <v>6</v>
+      </c>
+      <c r="K82" s="4">
         <f>COUNTIF(Table1[Senior Men],TRUE)</f>
-        <v>37</v>
-      </c>
-      <c r="L85" s="5"/>
-      <c r="M85" s="5">
+        <v>35</v>
+      </c>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4">
         <f>SUM(Table1[Column2])</f>
-        <v>11820</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H86">
+        <v>11460</v>
+      </c>
+      <c r="N82" s="4">
+        <f>SUM(Table1[paid or not])</f>
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H83">
         <f>4*8+2*3</f>
         <v>38</v>
       </c>
-      <c r="I86">
+      <c r="I83">
         <f>2*3+4*7</f>
         <v>34</v>
       </c>
-      <c r="K86">
+      <c r="K83">
         <f>3*3+7*4</f>
         <v>37</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="H2:K84">
+  <conditionalFormatting sqref="H2:K81">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -5255,12 +5503,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
-        <v>171</v>
+      <c r="A1" s="9" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="str" cm="1">
+      <c r="A2" s="8" t="str" cm="1">
         <f t="array" ref="A2:D38">_xlfn.CHOOSECOLS(_xlfn._xlws.FILTER(Table1[Name]:Table1[Senior Women],Table1[2nd &amp; Below]=TRUE),1,2,8,9)</f>
         <v>Le Roux Strydom</v>
       </c>
@@ -5275,7 +5523,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="str">
+      <c r="A3" s="8" t="str">
         <v>DJ Swanevelder</v>
       </c>
       <c r="B3" t="str">
@@ -5289,7 +5537,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="str">
+      <c r="A4" s="8" t="str">
         <v>Tian Louw</v>
       </c>
       <c r="B4" t="str">
@@ -5303,7 +5551,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="str">
+      <c r="A5" s="8" t="str">
         <v>Tazmin Harris</v>
       </c>
       <c r="B5" t="str">
@@ -5317,7 +5565,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="str">
+      <c r="A6" s="8" t="str">
         <v>Adam Domingo</v>
       </c>
       <c r="B6" t="str">
@@ -5331,7 +5579,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="str">
+      <c r="A7" s="8" t="str">
         <v>Allan Clark</v>
       </c>
       <c r="B7" t="str">
@@ -5345,7 +5593,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="str">
+      <c r="A8" s="8" t="str">
         <v>Quentin Thomas</v>
       </c>
       <c r="B8" t="str">
@@ -5359,8 +5607,8 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="str">
-        <v>Kirk Daries</v>
+      <c r="A9" s="8" t="str">
+        <v>Sedick Abrahams</v>
       </c>
       <c r="B9" t="str">
         <v>STEPH'S</v>
@@ -5373,11 +5621,11 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="str">
-        <v>Sedick Abrahams</v>
+      <c r="A10" s="8" t="str">
+        <v>Saaliegh Jabaar</v>
       </c>
       <c r="B10" t="str">
-        <v>STEPH'S</v>
+        <v>NEXUS</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -5387,8 +5635,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="str">
-        <v>Saaliegh Jabaar</v>
+      <c r="A11" s="8" t="str">
+        <v>Amien Phillips</v>
       </c>
       <c r="B11" t="str">
         <v>NEXUS</v>
@@ -5401,8 +5649,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="str">
-        <v>Amien Phillips</v>
+      <c r="A12" s="8" t="str">
+        <v>Timothy Sabad</v>
       </c>
       <c r="B12" t="str">
         <v>NEXUS</v>
@@ -5415,8 +5663,8 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="str">
-        <v>Timothy Sabad</v>
+      <c r="A13" s="8" t="str">
+        <v>Rafiq Tofa</v>
       </c>
       <c r="B13" t="str">
         <v>NEXUS</v>
@@ -5429,8 +5677,8 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="str">
-        <v>Rafiq Tofa</v>
+      <c r="A14" s="8" t="str">
+        <v>Craig Fortuin</v>
       </c>
       <c r="B14" t="str">
         <v>NEXUS</v>
@@ -5443,11 +5691,11 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="str">
-        <v>Craig Fortuin</v>
+      <c r="A15" s="8" t="str">
+        <v xml:space="preserve">Mujaid Hoffman </v>
       </c>
       <c r="B15" t="str">
-        <v>NEXUS</v>
+        <v>Community House</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
@@ -5457,8 +5705,8 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="str">
-        <v xml:space="preserve">Mujaid Hoffman </v>
+      <c r="A16" s="8" t="str">
+        <v>Lawrence Omadeli</v>
       </c>
       <c r="B16" t="str">
         <v>Community House</v>
@@ -5467,12 +5715,12 @@
         <v>1</v>
       </c>
       <c r="D16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="str">
-        <v>Lawrence Omadeli</v>
+      <c r="A17" s="8" t="str">
+        <v>Yusuf Ebrahim</v>
       </c>
       <c r="B17" t="str">
         <v>Community House</v>
@@ -5485,8 +5733,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="str">
-        <v>Yusuf Ebrahim</v>
+      <c r="A18" s="8" t="str">
+        <v>Felix Monday</v>
       </c>
       <c r="B18" t="str">
         <v>Community House</v>
@@ -5499,8 +5747,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="str">
-        <v>Felix Monday</v>
+      <c r="A19" s="8" t="str">
+        <v>Dave Sanusi</v>
       </c>
       <c r="B19" t="str">
         <v>Community House</v>
@@ -5513,8 +5761,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="str">
-        <v>Dave Sanusi</v>
+      <c r="A20" s="8" t="str">
+        <v>Janine Sait</v>
       </c>
       <c r="B20" t="str">
         <v>Community House</v>
@@ -5523,12 +5771,12 @@
         <v>1</v>
       </c>
       <c r="D20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="str">
-        <v>Janine Sait</v>
+      <c r="A21" s="8" t="str">
+        <v>Elijah Trout</v>
       </c>
       <c r="B21" t="str">
         <v>Community House</v>
@@ -5541,8 +5789,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="str">
-        <v>Elijah Trout</v>
+      <c r="A22" s="8" t="str">
+        <v>Lateef Samad</v>
       </c>
       <c r="B22" t="str">
         <v>Community House</v>
@@ -5555,22 +5803,22 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="str">
-        <v>Lateef Samad</v>
+      <c r="A23" s="8" t="str">
+        <v>Enrico Louw</v>
       </c>
       <c r="B23" t="str">
-        <v>Community House</v>
+        <v>Goodwood</v>
       </c>
       <c r="C23" t="b">
         <v>1</v>
       </c>
       <c r="D23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="str">
-        <v>Enrico Louw</v>
+      <c r="A24" s="8" t="str">
+        <v>Andre Taljaard</v>
       </c>
       <c r="B24" t="str">
         <v>Goodwood</v>
@@ -5583,8 +5831,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="str">
-        <v>Andre Taljaard</v>
+      <c r="A25" s="8" t="str">
+        <v>Delton Alexander</v>
       </c>
       <c r="B25" t="str">
         <v>Goodwood</v>
@@ -5593,12 +5841,12 @@
         <v>1</v>
       </c>
       <c r="D25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="str">
-        <v>Delton Alexander</v>
+      <c r="A26" s="8" t="str">
+        <v>Brendan o' Connell</v>
       </c>
       <c r="B26" t="str">
         <v>Goodwood</v>
@@ -5611,8 +5859,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="str">
-        <v>Brendan o' Connell</v>
+      <c r="A27" s="8" t="str">
+        <v>Pedro Fortuin</v>
       </c>
       <c r="B27" t="str">
         <v>Goodwood</v>
@@ -5621,29 +5869,29 @@
         <v>1</v>
       </c>
       <c r="D27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="str">
-        <v>Pedro Fortuin</v>
+      <c r="A28" s="8" t="str">
+        <v>Musfiquh Kalam</v>
       </c>
       <c r="B28" t="str">
-        <v>Goodwood</v>
+        <v xml:space="preserve">Boundary </v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
       </c>
       <c r="D28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="str">
-        <v>Musfiquh Kalam</v>
+      <c r="A29" s="8" t="str">
+        <v>Graham Van As</v>
       </c>
       <c r="B29" t="str">
-        <v xml:space="preserve">Boundary </v>
+        <v>Boundary</v>
       </c>
       <c r="C29" t="b">
         <v>1</v>
@@ -5653,11 +5901,11 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="str">
-        <v>Tamika Van Aa</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Boundary</v>
+      <c r="A30" s="8" t="str">
+        <v>Soso</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
       </c>
       <c r="C30" t="b">
         <v>1</v>
@@ -5667,25 +5915,25 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="str">
-        <v>Graham Van As</v>
+      <c r="A31" s="8" t="str">
+        <v>Ethan Hinrichsen</v>
       </c>
       <c r="B31" t="str">
-        <v>Boundary</v>
+        <v>UCT</v>
       </c>
       <c r="C31" t="b">
         <v>1</v>
       </c>
       <c r="D31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="str">
-        <v>Soso</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
+      <c r="A32" s="8" t="str">
+        <v>Llewellyn Bartlett</v>
+      </c>
+      <c r="B32" t="str">
+        <v>MP Royals</v>
       </c>
       <c r="C32" t="b">
         <v>1</v>
@@ -5695,22 +5943,22 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="str">
-        <v>Ethan Hinrichsen</v>
+      <c r="A33" s="8" t="str">
+        <v>Abubakr Manuel</v>
       </c>
       <c r="B33" t="str">
-        <v>UCT</v>
+        <v>MP Royals</v>
       </c>
       <c r="C33" t="b">
         <v>1</v>
       </c>
       <c r="D33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="str">
-        <v>Llewellyn Bartlett</v>
+      <c r="A34" s="8" t="str">
+        <v>Yaqeen Manuel</v>
       </c>
       <c r="B34" t="str">
         <v>MP Royals</v>
@@ -5724,7 +5972,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>Abubakr Manuel</v>
+        <v>Faeez Zoutenburg</v>
       </c>
       <c r="B35" t="str">
         <v>MP Royals</v>
@@ -5733,12 +5981,12 @@
         <v>1</v>
       </c>
       <c r="D35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>Yaqeen Manuel</v>
+        <v>Ilyaas Patel</v>
       </c>
       <c r="B36" t="str">
         <v>MP Royals</v>
@@ -5752,15 +6000,15 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>Ilyaas Patel</v>
+        <v>Kamiel Ebrahim</v>
       </c>
       <c r="B37" t="str">
-        <v>MP Royals</v>
+        <v>Mother City</v>
       </c>
       <c r="C37" t="b">
         <v>1</v>
       </c>
-      <c r="D37" t="b">
+      <c r="D37">
         <v>0</v>
       </c>
     </row>
@@ -5794,139 +6042,139 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="20"/>
+    <col min="2" max="2" width="9.140625" style="19"/>
     <col min="3" max="10" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="A1" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="14">
-        <v>1</v>
-      </c>
-      <c r="D2" s="14">
+      <c r="A2" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="13">
+        <v>1</v>
+      </c>
+      <c r="D2" s="13">
         <v>2</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="13">
         <v>3</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="13">
         <v>4</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="13">
         <v>5</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="13">
         <v>6</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
         <v>7</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="13">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>46171</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="18">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C3" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
+      <c r="C3" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
     </row>
     <row r="4" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>46171</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="18">
         <v>0.80208333333333337</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="E4" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="H4" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>198</v>
+      <c r="I4" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>194</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>46171</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <v>0.84375</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="F5" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="H5" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>198</v>
+      <c r="I5" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>194</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -5935,521 +6183,521 @@
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>46171</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <v>0.88541666666666663</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="G6" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>198</v>
+      <c r="I6" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>194</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>46171</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <v>0.92708333333333337</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
+      <c r="C7" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
+      <c r="A8" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>46172</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>46172</v>
+      </c>
+      <c r="B10" s="18">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="E10" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
         <v>46172</v>
       </c>
-      <c r="B10" s="19">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="B11" s="18">
+        <v>0.40625</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>46172</v>
+      </c>
+      <c r="B12" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <v>46172</v>
+      </c>
+      <c r="B13" s="18">
+        <v>0.5625</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="E13" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
         <v>46172</v>
       </c>
-      <c r="B11" s="19">
-        <v>0.40625</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="B14" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
         <v>46172</v>
       </c>
-      <c r="B12" s="19">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="G12" s="17" t="s">
+      <c r="B15" s="18">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="E15" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="F15" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="J12" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
-        <v>46172</v>
-      </c>
-      <c r="B13" s="19">
-        <v>0.5625</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
-        <v>46172</v>
-      </c>
-      <c r="B14" s="19">
-        <v>0.625</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
-        <v>46172</v>
-      </c>
-      <c r="B15" s="19">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="D15" s="16" t="s">
+      <c r="G15" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="H15" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="I15" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="J15" s="15" t="s">
         <v>110</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>113</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:15" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>46172</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <v>0.66666666666666696</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="G16" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="H16" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="I16" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="J16" s="15" t="s">
         <v>131</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>134</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>46172</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <v>0.6875</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F17" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="G17" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="H17" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="I17" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="J17" s="15" t="s">
         <v>159</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="J17" s="16" t="s">
-        <v>162</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>46172</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <v>0.70833333333333304</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>46172</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <v>0.72916666666666696</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="G19" s="17" t="s">
+      <c r="G19" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="16" t="s">
         <v>135</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>138</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>46172</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="18">
         <v>0.75</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
+      <c r="C20" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>46172</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <v>0.77083333333333404</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
+      <c r="C21" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>46172</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="18">
         <v>0.79166666666666696</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
+      <c r="C22" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>46172</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="18">
         <v>0.8125</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
+      <c r="C23" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>46172</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="18">
         <v>0.83333333333333404</v>
       </c>
-      <c r="C24" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
+      <c r="C24" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
     </row>
@@ -6532,7 +6780,7 @@
     <mergeCell ref="C24:J24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C4:J7 D12:J12 C12:C13 D13:G13 C14:H14 C15:J16 G17:J17 C17:F18 C19:J23 C9:J9 F10:J11 C10:E10 D11:E11">
+  <conditionalFormatting sqref="C4:J7 C9:J9 C10:E10 F10:J11 D11:E11 D12:J12 C12:C13 D13:G13 C14:H14 C15:J16 G17:J17 C17:F18 C19:J23">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="5th">
       <formula>NOT(ISERROR(SEARCH("5th",C4)))</formula>
     </cfRule>
